--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486692_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486692_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8163</v>
+        <v>4.0316</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4332</v>
+        <v>5.2264</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.617</v>
+        <v>-1.1948</v>
       </c>
       <c r="G2" t="n">
         <v>2.3146</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.4415</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.111</v>
+        <v>-0.3178</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5458</v>
+        <v>-0.1237</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6237</v>
+        <v>2.3568</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6365</v>
+        <v>1.4827</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0128</v>
+        <v>0.874</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0417</v>
+        <v>0.4738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2897</v>
+        <v>-2.5306</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7521</v>
+        <v>3.0045</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0779</v>
+        <v>2.8138</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3251</v>
+        <v>-1.6331</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7528</v>
+        <v>4.4469</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0362</v>
+        <v>-2.3399</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0354</v>
+        <v>-0.8975</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0008</v>
+        <v>-1.4424</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3696</v>
+        <v>0.4275</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.2764</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3702</v>
+        <v>0.7039</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9847</v>
+        <v>1.8415</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4554</v>
+        <v>1.8415</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0176</v>
+        <v>1.8335</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0691</v>
+        <v>4.1194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9485</v>
+        <v>-2.2859</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4738</v>
+        <v>2.0417</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5306</v>
+        <v>0.2897</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0045</v>
+        <v>1.7521</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8138</v>
+        <v>5.0779</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6331</v>
+        <v>1.3251</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4469</v>
+        <v>3.7528</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3399</v>
+        <v>-3.0362</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8975</v>
+        <v>-1.0354</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4424</v>
+        <v>-2.0008</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.4207</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6901</v>
+        <v>-0.5177</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7784</v>
+        <v>0.097</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8415</v>
+        <v>0.9847</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8415</v>
+        <v>2.4554</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9102</v>
+        <v>1.488</v>
       </c>
       <c r="E5" t="n">
         <v>1.9746</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0644</v>
+        <v>-0.4866</v>
       </c>
       <c r="G5" t="n">
         <v>0.8912</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1807</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>0.0825</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0982</v>
+        <v>0.6761</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5133</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6612</v>
+        <v>0.5826</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9833</v>
+        <v>0.8799</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.322</v>
+        <v>-0.2972</v>
       </c>
       <c r="G6" t="n">
         <v>0.5620000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6785</v>
+        <v>0.5999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.248</v>
+        <v>0.1446</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4305</v>
+        <v>0.4553</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2063</v>
+        <v>-0.0791</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9692</v>
+        <v>0.6589</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7628</v>
+        <v>-0.738</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7311</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4853</v>
+        <v>0.1999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3305</v>
+        <v>0.0202</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1548</v>
+        <v>0.1796</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Á. GONZÁLEZ CLEMENTE</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4069</v>
+        <v>-0.3984</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.3837</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4069</v>
+        <v>-0.0147</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4069</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.2213</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4069</v>
+        <v>1.1371</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.1242</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3858</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4069</v>
+        <v>-0.5942</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.3454</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4069</v>
+        <v>-0.2487</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.4413</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2485</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.1928</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>Á. GONZÁLEZ CLEMENTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1101</v>
+        <v>-0.4069</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7974</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3127</v>
+        <v>-0.4069</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9157999999999999</v>
+        <v>-0.4069</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2213</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1371</v>
+        <v>-0.4069</v>
       </c>
       <c r="J9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1242</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3858</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5942</v>
+        <v>-0.4069</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3454</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2487</v>
+        <v>-0.4069</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.153</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6622</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4908</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4196</v>
+        <v>-1.9355</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0241</v>
+        <v>-0.7138</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3955</v>
+        <v>-1.2217</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4321</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9875</v>
+        <v>-0.5034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8277</v>
+        <v>-0.5175</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1598</v>
+        <v>0.014</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4619</v>
+        <v>-4.6357</v>
       </c>
       <c r="E11" t="n">
         <v>-3.3525</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1094</v>
+        <v>-1.2832</v>
       </c>
       <c r="G11" t="n">
         <v>-2.629</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8329</v>
+        <v>-1.0067</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4415</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3914</v>
+        <v>-0.5653</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.836799999999999</v>
+        <v>2.836899999999999</v>
       </c>
       <c r="E12" t="n">
         <v>9.8919</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.055</v>
+        <v>-7.055000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -1390,13 +1390,13 @@
         <v>13.5154</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8277000000000001</v>
+        <v>-0.8277</v>
       </c>
       <c r="T12" t="n">
         <v>-2.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2443</v>
+        <v>1.2441</v>
       </c>
       <c r="V12" t="n">
         <v>0.6990999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5542</v>
+        <v>4.5449</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7865</v>
+        <v>3.7523</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7678</v>
+        <v>0.7926</v>
       </c>
       <c r="G13" t="n">
         <v>2.5795</v>
@@ -1468,13 +1468,13 @@
         <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9747</v>
+        <v>0.9654</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6822</v>
+        <v>0.6479</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2926</v>
+        <v>0.3174</v>
       </c>
       <c r="V13" t="n">
         <v>0.6138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.725</v>
+        <v>3.0837</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1127</v>
+        <v>3.5956</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3877</v>
+        <v>-0.5119</v>
       </c>
       <c r="G14" t="n">
         <v>2.0682</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4137</v>
+        <v>-0.2275</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2201</v>
+        <v>-0.297</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1936</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.8568</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.428</v>
+        <v>2.0639</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8023</v>
+        <v>1.3886</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6256</v>
+        <v>0.6753</v>
       </c>
       <c r="G15" t="n">
         <v>0.9509</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3845</v>
+        <v>1.0205</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9375</v>
+        <v>0.5238</v>
       </c>
       <c r="U15" t="n">
-        <v>0.447</v>
+        <v>0.4967</v>
       </c>
       <c r="V15" t="n">
         <v>0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1429</v>
+        <v>1.2048</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2063</v>
+        <v>3.5166</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0635</v>
+        <v>-2.3118</v>
       </c>
       <c r="G16" t="n">
         <v>0.9122</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8273</v>
+        <v>-0.7653</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.214</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3867</v>
+        <v>0.1384</v>
       </c>
       <c r="V16" t="n">
         <v>0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8601</v>
+        <v>0.1329</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3735</v>
+        <v>0.2471</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4867</v>
+        <v>-0.1142</v>
       </c>
       <c r="G17" t="n">
         <v>2.3357</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7171999999999999</v>
+        <v>0.2758</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5518</v>
+        <v>0.0687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1654</v>
+        <v>0.2071</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0002</v>
+        <v>-0.9754</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1104</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8898</v>
+        <v>-0.865</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8138</v>
@@ -1858,13 +1858,13 @@
         <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4236</v>
+        <v>-2.4566</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2907</v>
+        <v>-2.4976</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1329</v>
+        <v>0.0409</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7254</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3364</v>
+        <v>0.3034</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3584</v>
+        <v>0.1515</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.022</v>
+        <v>0.1518</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7672</v>
+        <v>-2.544</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2388</v>
+        <v>-1.6183</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5284</v>
+        <v>-0.9257</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5196</v>
@@ -2014,13 +2014,13 @@
         <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3748</v>
+        <v>-0.1515</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.214</v>
+        <v>-0.5935</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.4419</v>
       </c>
       <c r="V20" t="n">
         <v>2.1271</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0054</v>
+        <v>-3.5669</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1718</v>
+        <v>-1.7582</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8335</v>
+        <v>-1.8087</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6845</v>
@@ -2092,13 +2092,13 @@
         <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2316</v>
+        <v>0.2069</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5245</v>
+        <v>-0.1108</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2929</v>
+        <v>0.3178</v>
       </c>
       <c r="V21" t="n">
         <v>0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6302</v>
+        <v>-4.324</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3325</v>
+        <v>0.5393</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9627</v>
+        <v>-4.8634</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1032</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0371</v>
+        <v>-0.7309</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8277</v>
+        <v>-0.6209</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2093</v>
+        <v>-0.11</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6831</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.836600000000001</v>
+        <v>-2.836699999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>7.055100000000001</v>
+        <v>7.054999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.8918</v>
+        <v>-9.8919</v>
       </c>
       <c r="G23" t="n">
         <v>-1.999999999999998</v>
@@ -2248,13 +2248,13 @@
         <v>12.5502</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8274999999999997</v>
+        <v>0.8278</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2442</v>
+        <v>-1.2444</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0719</v>
+        <v>2.072</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6993</v>
